--- a/TEngine/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/__enums__.xlsx
@@ -529,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -778,6 +778,57 @@
         <v>44</v>
       </c>
     </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy.ETrophyUnlockType</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯解锁条件</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AllDailyChallengesInMonth</t>
+        </is>
+      </c>
+      <c r="J15" s="0">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成当月全部每日挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DailyChallengeCountInMonth</t>
+        </is>
+      </c>
+      <c r="J16" s="0">
+        <v>2</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成当月指定天数，条件值填写所需天数</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
